--- a/doc/cols_por_archivo.xlsx
+++ b/doc/cols_por_archivo.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="227">
   <si>
     <t xml:space="preserve">Titulo </t>
   </si>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">Comentario </t>
   </si>
   <si>
-    <t>Opciones</t>
+    <t>Observaciones</t>
   </si>
   <si>
     <t>Prospeccion/Lead</t>
@@ -53,6 +53,9 @@
     <t>" = company" &amp; content_object_id</t>
   </si>
   <si>
+    <t>Listo</t>
+  </si>
+  <si>
     <t>Leadas_cargados</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
     <t>Primer contacto</t>
   </si>
   <si>
+    <t xml:space="preserve">Listo </t>
+  </si>
+  <si>
     <t>Total interacciones</t>
   </si>
   <si>
@@ -86,6 +92,9 @@
     <t xml:space="preserve">prospectos interesados </t>
   </si>
   <si>
+    <t>falta</t>
+  </si>
+  <si>
     <t>contactos efecitvos</t>
   </si>
   <si>
@@ -95,7 +104,7 @@
     <t>connected</t>
   </si>
   <si>
-    <t>Listo</t>
+    <t>Llenado de herramienta</t>
   </si>
   <si>
     <t>inversion en prospeccion</t>
@@ -116,12 +125,19 @@
     <t>deal_source</t>
   </si>
   <si>
+    <t>Llenado de herramienta
+llenado de la herramienta</t>
+  </si>
+  <si>
     <t>Inversion x Canal</t>
   </si>
   <si>
     <t>Leads calificados actuales</t>
   </si>
   <si>
+    <t>llenado de la herramienta</t>
+  </si>
+  <si>
     <t>Leadas Calificados mes anterior</t>
   </si>
   <si>
@@ -149,6 +165,9 @@
     <t>en el stageadecuado</t>
   </si>
   <si>
+    <t>Cuadro de tiempos</t>
+  </si>
+  <si>
     <t>Propuestas rechazadas</t>
   </si>
   <si>
@@ -203,6 +222,9 @@
     <t xml:space="preserve">valor inicial </t>
   </si>
   <si>
+    <t>Falta</t>
+  </si>
+  <si>
     <t>abandonadas</t>
   </si>
   <si>
@@ -267,6 +289,9 @@
   </si>
   <si>
     <t>cliente satisfecho</t>
+  </si>
+  <si>
+    <t>Nuevos datos Yeni</t>
   </si>
   <si>
     <t>clientes totales</t>
@@ -692,13 +717,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -819,19 +844,19 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
@@ -846,7 +871,7 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
@@ -855,7 +880,7 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -864,16 +889,16 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1228,7 +1253,7 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
       <c r="A1" s="18" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B1" s="19">
         <v>0</v>
@@ -1341,46 +1366,46 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I2" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O2" s="21"/>
       <c r="P2" s="21"/>
@@ -1408,58 +1433,58 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I3" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="O3" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="P3" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="K3" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="L3" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="N3" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="O3" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="P3" s="20" t="s">
-        <v>101</v>
-      </c>
       <c r="Q3" s="20" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="R3" s="20" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="S3" s="21"/>
       <c r="T3" s="21"/>
@@ -1483,91 +1508,91 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="M4" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="N4" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="P4" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q4" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="R4" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="S4" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="J4" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="M4" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="N4" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="O4" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P4" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q4" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="R4" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="S4" s="20" t="s">
-        <v>108</v>
-      </c>
       <c r="T4" s="20" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="U4" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V4" s="20" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="W4" s="20" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="X4" s="20" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="Y4" s="20" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="Z4" s="20" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="AA4" s="20" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="AB4" s="20" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="AC4" s="20" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AD4" s="21"/>
       <c r="AE4" s="21"/>
@@ -1580,25 +1605,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H5" s="21"/>
       <c r="I5" s="21"/>
@@ -1633,91 +1658,91 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K6" s="20" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="M6" s="20" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="N6" s="20" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="R6" s="20" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="S6" s="20" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="T6" s="20" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="U6" s="20" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="V6" s="20" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="W6" s="20" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="X6" s="20" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="Y6" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z6" s="20" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="AA6" s="20" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="AB6" s="20" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AC6" s="20" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AD6" s="21"/>
       <c r="AE6" s="21"/>
@@ -1730,19 +1755,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="F7" s="21"/>
       <c r="G7" s="21"/>
@@ -1779,55 +1804,55 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E8" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="O8" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="F8" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="K8" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="L8" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="N8" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="O8" s="20" t="s">
-        <v>158</v>
-      </c>
       <c r="P8" s="20" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="R8" s="21"/>
       <c r="S8" s="21"/>
@@ -1852,25 +1877,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H9" s="21"/>
       <c r="I9" s="21"/>
@@ -1905,22 +1930,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
@@ -1956,19 +1981,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F11" s="21"/>
       <c r="G11" s="21"/>
@@ -2005,25 +2030,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H12" s="21"/>
       <c r="I12" s="21"/>
@@ -2058,25 +2083,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="H13" s="21"/>
       <c r="I13" s="21"/>
@@ -2111,138 +2136,138 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="I14" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="M14" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="J14" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="K14" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="L14" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="M14" s="20" t="s">
-        <v>95</v>
-      </c>
       <c r="N14" s="20" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="P14" s="20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q14" s="20" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="R14" s="20" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="S14" s="20" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="T14" s="20" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="U14" s="20" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="V14" s="20" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="W14" s="20" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="X14" s="20" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="Y14" s="20" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="Z14" s="20" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="AA14" s="20" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="AB14" s="20" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AC14" s="20" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AD14" s="20" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="AE14" s="20" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="AF14" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="AG14" s="20" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="AH14" s="20" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="AI14" s="20" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="AJ14" s="20" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AK14" s="20" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="21"/>
@@ -2277,46 +2302,46 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="M16" s="20" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="N16" s="20" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="O16" s="21"/>
       <c r="P16" s="21"/>
@@ -2355,12 +2380,12 @@
   <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="21.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="16" width="29.005" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="16" width="36.005" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="17" width="22.14785714285714" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="17" width="21.719285714285714" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="17" width="42.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="17" width="17.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="17" width="27.719285714285714" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -2368,7 +2393,7 @@
     <col min="11" max="11" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2409,7 +2434,9 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -2421,16 +2448,18 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -2442,18 +2471,20 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -2465,18 +2496,20 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2488,12 +2521,14 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -2505,19 +2540,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>23</v>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -2530,12 +2565,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -2544,36 +2581,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -2582,32 +2623,36 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="37.5">
       <c r="A12" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -2616,15 +2661,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="6"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -2633,21 +2680,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -2656,21 +2705,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -2679,21 +2730,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -2702,22 +2755,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -2725,23 +2778,25 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -2750,21 +2805,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -2773,21 +2830,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -2796,15 +2855,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="F21" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -2813,22 +2874,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -2838,44 +2899,48 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F23" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -2884,44 +2949,48 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -2930,21 +2999,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="12" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -2953,21 +3024,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -2976,21 +3049,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -2999,21 +3074,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -3022,19 +3099,21 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -3043,19 +3122,21 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
+      <c r="F32" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -3064,15 +3145,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
       <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
+      <c r="F33" s="15" t="s">
+        <v>90</v>
+      </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15"/>
       <c r="I33" s="15"/>
@@ -3081,15 +3164,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C34" s="15"/>
       <c r="D34" s="15"/>
       <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
+      <c r="F34" s="15" t="s">
+        <v>90</v>
+      </c>
       <c r="G34" s="15"/>
       <c r="H34" s="15"/>
       <c r="I34" s="15"/>
@@ -3098,15 +3183,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
       <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
+      <c r="F35" s="15" t="s">
+        <v>90</v>
+      </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15"/>
       <c r="I35" s="15"/>
@@ -3115,15 +3202,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C36" s="15"/>
       <c r="D36" s="15"/>
       <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
+      <c r="F36" s="15" t="s">
+        <v>90</v>
+      </c>
       <c r="G36" s="15"/>
       <c r="H36" s="15"/>
       <c r="I36" s="15"/>
@@ -3132,21 +3221,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F37" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -3155,15 +3246,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C38" s="15"/>
       <c r="D38" s="15"/>
       <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
+      <c r="F38" s="15" t="s">
+        <v>90</v>
+      </c>
       <c r="G38" s="15"/>
       <c r="H38" s="15"/>
       <c r="I38" s="15"/>
@@ -3172,15 +3265,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="15"/>
       <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
+      <c r="F39" s="15" t="s">
+        <v>90</v>
+      </c>
       <c r="G39" s="15"/>
       <c r="H39" s="15"/>
       <c r="I39" s="15"/>
@@ -3189,15 +3284,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="F40" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
